--- a/docs/oc-regiones/alimentos/magallanes.xlsx
+++ b/docs/oc-regiones/alimentos/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1432,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1619,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1867,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2054,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2119,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2835,7 +2863,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4083,7 +4115,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5067,7 +5103,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5128,7 +5168,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5250,7 +5294,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5868,7 +5916,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5929,7 +5981,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6368,7 +6424,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6860,7 +6920,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7665,7 +7729,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8035,7 +8103,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8462,7 +8534,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8954,7 +9030,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9511,7 +9591,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9702,7 +9786,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10023,7 +10111,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10084,7 +10176,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10145,7 +10241,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10775,7 +10875,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10962,7 +11066,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11283,7 +11391,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11409,7 +11521,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11600,7 +11716,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11848,7 +11968,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11974,7 +12098,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12035,7 +12163,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12096,7 +12228,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12661,7 +12797,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13299,7 +13439,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13360,7 +13504,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13421,7 +13569,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13608,7 +13760,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14551,7 +14707,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14612,7 +14772,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14799,7 +14963,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15494,7 +15662,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15555,7 +15727,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15933,7 +16109,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16189,7 +16369,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16567,7 +16751,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16754,7 +16942,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16880,7 +17072,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17823,7 +18019,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17884,7 +18084,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17945,7 +18149,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18193,7 +18401,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18701,7 +18913,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19213,7 +19429,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20172,7 +20392,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20489,7 +20713,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20550,7 +20778,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20737,7 +20969,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20798,7 +21034,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21420,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22704,7 +22948,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22830,7 +23078,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22956,7 +23208,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23334,7 +23590,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23395,7 +23655,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23586,7 +23850,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24090,7 +24358,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24346,7 +24618,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24773,7 +25049,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25838,7 +26118,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26090,7 +26374,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26277,7 +26565,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26525,7 +26817,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26964,7 +27260,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27915,7 +28215,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27976,7 +28280,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28602,7 +28910,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29305,7 +29617,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30065,7 +30381,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30382,7 +30702,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30825,7 +31149,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30947,7 +31275,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31764,7 +32096,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32512,7 +32848,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33138,7 +33478,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33386,7 +33730,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33760,7 +34108,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33821,7 +34173,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34329,7 +34685,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34516,7 +34876,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34577,7 +34941,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36032,7 +36400,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36349,7 +36721,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +37237,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37300,7 +37680,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37552,7 +37936,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38247,7 +38635,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38682,7 +39074,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38930,7 +39326,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39235,7 +39635,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39617,7 +40021,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39869,7 +40277,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39930,7 +40342,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40056,7 +40472,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40629,7 +41049,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40816,7 +41240,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41068,7 +41496,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41259,7 +41691,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42007,7 +42443,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42068,7 +42508,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42511,7 +42955,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42950,7 +43398,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43202,7 +43654,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43263,7 +43719,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43324,7 +43784,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43824,7 +44288,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44836,7 +45304,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44897,7 +45369,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44958,7 +45434,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45836,7 +46316,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47295,7 +47779,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47356,7 +47844,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47539,7 +48031,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47986,7 +48482,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48616,7 +49116,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49372,7 +49876,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49498,7 +50006,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50250,7 +50762,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50563,7 +51079,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50685,7 +51205,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51002,7 +51526,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51514,7 +52042,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51575,7 +52107,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51888,7 +52424,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52140,7 +52680,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52323,7 +52867,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52766,7 +53314,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52888,7 +53440,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53010,7 +53566,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53136,7 +53696,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54209,7 +54773,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54644,7 +55212,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55205,7 +55777,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55392,7 +55968,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55579,7 +56159,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56197,7 +56781,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56506,7 +57094,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57339,7 +57931,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57587,7 +58183,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57839,7 +58439,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58091,7 +58695,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L919" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58152,7 +58760,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58660,7 +59272,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59408,7 +60024,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59843,7 +60463,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59969,7 +60593,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61863,7 +62491,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62440,7 +63072,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L988" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62753,7 +63389,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63005,7 +63645,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64842,7 +65486,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1026" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64903,7 +65551,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65655,7 +66307,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1039" t="inlineStr"/>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1039" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65972,7 +66628,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1044" t="inlineStr"/>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1044" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66736,7 +67396,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1056" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67106,7 +67770,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1062" t="inlineStr"/>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1062" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67167,7 +67835,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1063" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67419,7 +68091,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1067" t="inlineStr"/>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1067" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67545,7 +68221,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1069" t="inlineStr"/>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1069" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67606,7 +68286,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1070" t="inlineStr"/>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1070" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67858,7 +68542,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1074" t="inlineStr"/>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1074" t="inlineStr">
         <is>
           <t>USD</t>
